--- a/essence/EA_Alpha_Assessment.xlsx
+++ b/essence/EA_Alpha_Assessment.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="438">
   <si>
     <t xml:space="preserve">Essence Alpha Assessment</t>
   </si>
@@ -612,91 +612,121 @@
     <t xml:space="preserve">Architecture Selected</t>
   </si>
   <si>
-    <t xml:space="preserve">An architecture is selected that addresses the key technical risks.</t>
+    <t xml:space="preserve">The architecture's key concepts and properties are clearly defined.</t>
   </si>
   <si>
     <t xml:space="preserve">Demonstrable</t>
   </si>
   <si>
-    <t xml:space="preserve">The build / buy / configure decisions are made.</t>
+    <t xml:space="preserve">The selected architecture is clearly conceived.</t>
   </si>
   <si>
     <t xml:space="preserve">Usable</t>
   </si>
   <si>
-    <t xml:space="preserve">The technology and platform decisions are agreed with stakeholders.</t>
+    <t xml:space="preserve">The system boundary is known.</t>
   </si>
   <si>
     <t xml:space="preserve">Ready</t>
   </si>
   <si>
+    <t xml:space="preserve">Significant decisions about the system's organization have been made.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy, build, and reuse decisions have been made.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retired</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The key technical risks are agreed.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2. Demonstrable</t>
   </si>
   <si>
-    <t xml:space="preserve">The key architectural characteristics are demonstrated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The relevant stakeholders agree the architecture is appropriate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retired</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The critical interfaces and integrations have been exercised.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Performance has been measured against the key drivers.</t>
+    <t xml:space="preserve">The key architectural characteristics have been demonstrated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system can be exercised and its performance measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critical configurations of the architecture have been demonstrated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critical interfaces have been demonstrated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration with other existing systems has been demonstrated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relevant stakeholders agree the demonstrated architecture is appropriate.</t>
   </si>
   <si>
     <t xml:space="preserve">3. Usable</t>
   </si>
   <si>
-    <t xml:space="preserve">The system can be operated by representative users.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The functionality has been demonstrated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The performance and defect levels are acceptable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A usable system is available.</t>
+    <t xml:space="preserve">The system can be operated by the stakeholders who use it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The functionality provided by the system has been tested.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system's performance is acceptable to the stakeholders.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defect levels are acceptable to the stakeholders.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system is sufficiently documented.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The released system elements are known.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The added value provided by the system is clear.</t>
   </si>
   <si>
     <t xml:space="preserve">4. Ready</t>
   </si>
   <si>
-    <t xml:space="preserve">The system has passed the agreed tests.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operational and support documentation is available.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The stakeholder representatives accept the system.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The system is ready for deployment.</t>
+    <t xml:space="preserve">Documentation on deploying and using the system in its intended environment is available.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The stakeholder representatives accept the system as fit-for-purpose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The stakeholder representatives want to make the system available for use.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operational support is in place.</t>
   </si>
   <si>
     <t xml:space="preserve">5. Operational</t>
   </si>
   <si>
-    <t xml:space="preserve">The system is in use in the operational environment.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The system is supported to the agreed service levels.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The system is available to its intended users.</t>
+    <t xml:space="preserve">The system has been made available to its intended stakeholders.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At least one instance of the system is fully operational.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system is fully supported to the agreed service levels.</t>
   </si>
   <si>
     <t xml:space="preserve">6. Retired</t>
   </si>
   <si>
+    <t xml:space="preserve">The system has been replaced or discontinued.</t>
+  </si>
+  <si>
     <t xml:space="preserve">The system is no longer supported.</t>
   </si>
   <si>
-    <t xml:space="preserve">The system has been replaced or removed from operation.</t>
+    <t xml:space="preserve">There are no official stakeholders still using the system.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Updates to the system will no longer be produced.</t>
   </si>
   <si>
     <t xml:space="preserve">The activity and effort applied to produce the result.</t>
@@ -1345,10 +1375,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-    <numFmt numFmtId="166" formatCode="0%"/>
+    <numFmt numFmtId="165" formatCode="0%"/>
   </numFmts>
   <fonts count="53">
     <font>
@@ -2004,6 +2033,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2024,11 +2057,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2068,7 +2097,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2188,7 +2217,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="34" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="34" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2236,7 +2265,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="40" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="40" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2272,7 +2301,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="43" fillId="7" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="43" fillId="7" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2296,7 +2325,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="47" fillId="8" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="47" fillId="8" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2320,7 +2349,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="51" fillId="19" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="51" fillId="19" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2657,77 +2686,77 @@
   <dimension ref="B1:O29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="15" min="15" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="15" min="15" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O1" s="0" t="n">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="O1" s="1" t="n">
         <f aca="false">O4/O5</f>
-        <v>0.604761904761905</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="O3" s="0" t="n">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="O3" s="1" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O4" s="0" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="O4" s="1" t="n">
         <f aca="false">Opportunity!M1+Stakeholders!M1+'Business Scenario'!M1+'Service Blueprint'!M1+Requirements!M1+System!M1+'Architectural Drivers'!M1+Architecture!M1+'Architecture Decisions'!M1+'Paved Road'!M1+Work!M1+Team!M1+'Way of Working'!M1+Governance!M1</f>
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4" t="s">
+      <c r="C5" s="4"/>
+      <c r="D5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="5" t="s">
+      <c r="E5" s="5"/>
+      <c r="F5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="O5" s="6" t="n">
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="O5" s="1" t="n">
         <f aca="false">Opportunity!M2+Stakeholders!M2+'Business Scenario'!M2+'Service Blueprint'!M2+Requirements!M2+System!M2+'Architectural Drivers'!M2+Architecture!M2+'Architecture Decisions'!M2+'Paved Road'!M2+Work!M2+Team!M2+'Way of Working'!M2+Governance!M2</f>
-        <v>210</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="n">
         <f aca="false">O1</f>
-        <v>0.604761904761905</v>
+        <v>0.55</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="8" t="str">
@@ -2737,7 +2766,7 @@
       <c r="E6" s="8"/>
       <c r="F6" s="9" t="str">
         <f aca="false">O4&amp;" / "&amp;O5</f>
-        <v>127 / 210</v>
+        <v>121 / 220</v>
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
@@ -2929,18 +2958,18 @@
       </c>
       <c r="E16" s="16" t="str">
         <f aca="false">System!B5</f>
-        <v>Architecture Selected</v>
+        <v>Not started</v>
       </c>
       <c r="F16" s="17" t="n">
         <f aca="false">System!C5</f>
-        <v>0.285714285714286</v>
+        <v>0</v>
       </c>
       <c r="G16" s="18" t="s">
         <v>29</v>
       </c>
       <c r="H16" s="19" t="str">
         <f aca="false">IF(F16&gt;=1,"✔ Complete",IF(F16&gt;0,"● In progress","○ Not started"))</f>
-        <v>● In progress</v>
+        <v>○ Not started</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3173,7 +3202,7 @@
       <c r="G27" s="29"/>
       <c r="H27" s="29"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="30" t="s">
         <v>51</v>
       </c>
@@ -3184,7 +3213,7 @@
       <c r="G28" s="30"/>
       <c r="H28" s="30"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="31" t="s">
         <v>52</v>
       </c>
@@ -3214,7 +3243,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{16CE96D6-646A-48AB-85A6-EEB8F32036D9}</x14:id>
+          <x14:id>{73698B5B-2020-4350-80CB-CA90B8224CA3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3258,7 +3287,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{16CE96D6-646A-48AB-85A6-EEB8F32036D9}">
+          <x14:cfRule type="dataBar" id="{73698B5B-2020-4350-80CB-CA90B8224CA3}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -3287,19 +3316,19 @@
   <dimension ref="B1:M16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="6" t="n">
+      <c r="M1" s="1" t="n">
         <f aca="false">SUM(H7:H11)</f>
         <v>7</v>
       </c>
@@ -3313,19 +3342,19 @@
       <c r="E2" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="M2" s="1" t="n">
         <f aca="false">SUM(I7:I11)</f>
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="44" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="1" t="n">
         <f aca="false">SUM(K7:K11)</f>
         <v>3</v>
       </c>
@@ -3343,7 +3372,7 @@
       <c r="E4" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="1" t="n">
         <f aca="false">SUM(J7:J11)</f>
         <v>3</v>
       </c>
@@ -3362,7 +3391,7 @@
         <v>3 / 5</v>
       </c>
       <c r="E5" s="60" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3387,27 +3416,27 @@
         <v>72</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="E7" s="53" t="str">
         <f aca="false">COUNTIF(C7:C8,"✔")&amp;" / 2"</f>
         <v>2 / 2</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="1" t="n">
         <f aca="false">COUNTIF(C7:C8,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="1" t="n">
         <f aca="false">IF(H7=I7,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="1" t="n">
         <f aca="false">J7</f>
         <v>1</v>
       </c>
@@ -3418,57 +3447,57 @@
         <v>72</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="E8" s="53"/>
-      <c r="G8" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="H8" s="6" t="n">
+      <c r="G8" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="H8" s="1" t="n">
         <f aca="false">COUNTIF(C9:C10,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="1" t="n">
         <f aca="false">IF(H8=I8,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="1" t="n">
         <f aca="false">J8*K7</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="61" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="C9" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="E9" s="53" t="str">
         <f aca="false">COUNTIF(C9:C10,"✔")&amp;" / 2"</f>
         <v>2 / 2</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="H9" s="6" t="n">
+      <c r="G9" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <f aca="false">COUNTIF(C11:C12,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="1" t="n">
         <f aca="false">IF(H9=I9,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="1" t="n">
         <f aca="false">J9*K8</f>
         <v>1</v>
       </c>
@@ -3479,57 +3508,57 @@
         <v>72</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="E10" s="53"/>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="1" t="n">
         <f aca="false">COUNTIF(C13:C14,"✔")</f>
         <v>1</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="1" t="n">
         <f aca="false">IF(H10=I10,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="1" t="n">
         <f aca="false">J10*K9</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="61" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="C11" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="E11" s="53" t="str">
         <f aca="false">COUNTIF(C11:C12,"✔")&amp;" / 2"</f>
         <v>2 / 2</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="1" t="n">
         <f aca="false">COUNTIF(C15:C16,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="1" t="n">
         <f aca="false">IF(H11=I11,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="1" t="n">
         <f aca="false">J11*K10</f>
         <v>0</v>
       </c>
@@ -3540,19 +3569,19 @@
         <v>72</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="E12" s="53"/>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="61" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="C13" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="E13" s="53" t="str">
         <f aca="false">COUNTIF(C13:C14,"✔")&amp;" / 2"</f>
@@ -3563,17 +3592,17 @@
       <c r="B14" s="61"/>
       <c r="C14" s="54"/>
       <c r="D14" s="55" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E14" s="53"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="61" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="C15" s="51"/>
       <c r="D15" s="52" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="E15" s="53" t="str">
         <f aca="false">COUNTIF(C15:C16,"✔")&amp;" / 2"</f>
@@ -3584,7 +3613,7 @@
       <c r="B16" s="61"/>
       <c r="C16" s="54"/>
       <c r="D16" s="55" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="E16" s="53"/>
     </row>
@@ -3661,19 +3690,19 @@
   <dimension ref="B1:M17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="6" t="n">
+      <c r="M1" s="1" t="n">
         <f aca="false">SUM(H7:H12)</f>
         <v>7</v>
       </c>
@@ -3687,19 +3716,19 @@
       <c r="E2" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="M2" s="1" t="n">
         <f aca="false">SUM(I7:I12)</f>
         <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="44" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="1" t="n">
         <f aca="false">SUM(K7:K12)</f>
         <v>3</v>
       </c>
@@ -3717,7 +3746,7 @@
       <c r="E4" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="1" t="n">
         <f aca="false">SUM(J7:J12)</f>
         <v>3</v>
       </c>
@@ -3736,7 +3765,7 @@
         <v>3 / 6</v>
       </c>
       <c r="E5" s="60" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3755,33 +3784,33 @@
     </row>
     <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="61" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="C7" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="E7" s="53" t="str">
         <f aca="false">COUNTIF(C7:C8,"✔")&amp;" / 2"</f>
         <v>2 / 2</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="H7" s="6" t="n">
+      <c r="G7" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H7" s="1" t="n">
         <f aca="false">COUNTIF(C7:C8,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="1" t="n">
         <f aca="false">IF(H7=I7,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="1" t="n">
         <f aca="false">J7</f>
         <v>1</v>
       </c>
@@ -3792,57 +3821,57 @@
         <v>72</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="E8" s="53"/>
-      <c r="G8" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="H8" s="6" t="n">
+      <c r="G8" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="H8" s="1" t="n">
         <f aca="false">COUNTIF(C9:C10,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="1" t="n">
         <f aca="false">IF(H8=I8,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="1" t="n">
         <f aca="false">J8*K7</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="61" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C9" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="E9" s="53" t="str">
         <f aca="false">COUNTIF(C9:C10,"✔")&amp;" / 2"</f>
         <v>2 / 2</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="H9" s="6" t="n">
+      <c r="G9" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <f aca="false">COUNTIF(C11:C12,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="1" t="n">
         <f aca="false">IF(H9=I9,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="1" t="n">
         <f aca="false">J9*K8</f>
         <v>1</v>
       </c>
@@ -3853,57 +3882,57 @@
         <v>72</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="E10" s="53"/>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="1" t="n">
         <f aca="false">COUNTIF(C13:C14,"✔")</f>
         <v>1</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="1" t="n">
         <f aca="false">IF(H10=I10,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="1" t="n">
         <f aca="false">J10*K9</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="61" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C11" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="E11" s="53" t="str">
         <f aca="false">COUNTIF(C11:C12,"✔")&amp;" / 2"</f>
         <v>2 / 2</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="1" t="n">
         <f aca="false">COUNTIF(C15:C15,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="1" t="n">
         <f aca="false">IF(H11=I11,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="1" t="n">
         <f aca="false">J11*K10</f>
         <v>0</v>
       </c>
@@ -3914,37 +3943,37 @@
         <v>72</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="E12" s="53"/>
-      <c r="G12" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="H12" s="6" t="n">
+      <c r="G12" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="H12" s="1" t="n">
         <f aca="false">COUNTIF(C16:C17,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I12" s="0" t="n">
+      <c r="I12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="1" t="n">
         <f aca="false">IF(H12=I12,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="K12" s="1" t="n">
         <f aca="false">J12*K11</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="61" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="C13" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="E13" s="53" t="str">
         <f aca="false">COUNTIF(C13:C14,"✔")&amp;" / 2"</f>
@@ -3955,17 +3984,17 @@
       <c r="B14" s="61"/>
       <c r="C14" s="54"/>
       <c r="D14" s="55" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="E14" s="53"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="61" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="C15" s="51"/>
       <c r="D15" s="52" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="E15" s="62" t="str">
         <f aca="false">COUNTIF(C15:C15,"✔")&amp;" / 1"</f>
@@ -3974,11 +4003,11 @@
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="61" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="C16" s="54"/>
       <c r="D16" s="55" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="E16" s="53" t="str">
         <f aca="false">COUNTIF(C16:C17,"✔")&amp;" / 2"</f>
@@ -3989,7 +4018,7 @@
       <c r="B17" s="61"/>
       <c r="C17" s="51"/>
       <c r="D17" s="52" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="E17" s="53"/>
     </row>
@@ -4071,19 +4100,19 @@
   <dimension ref="B1:M11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="6" t="n">
+      <c r="M1" s="1" t="n">
         <f aca="false">SUM(H7:H11)</f>
         <v>4</v>
       </c>
@@ -4097,19 +4126,19 @@
       <c r="E2" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="M2" s="1" t="n">
         <f aca="false">SUM(I7:I11)</f>
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="44" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="1" t="n">
         <f aca="false">SUM(K7:K11)</f>
         <v>4</v>
       </c>
@@ -4127,7 +4156,7 @@
       <c r="E4" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="1" t="n">
         <f aca="false">SUM(J7:J11)</f>
         <v>4</v>
       </c>
@@ -4146,7 +4175,7 @@
         <v>4 / 5</v>
       </c>
       <c r="E5" s="60" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4165,163 +4194,163 @@
     </row>
     <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="61" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="C7" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="E7" s="62" t="str">
         <f aca="false">COUNTIF(C7:C7,"✔")&amp;" / 1"</f>
         <v>1 / 1</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="H7" s="6" t="n">
+      <c r="G7" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="H7" s="1" t="n">
         <f aca="false">COUNTIF(C7:C7,"✔")</f>
         <v>1</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="1" t="n">
         <f aca="false">IF(H7=I7,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="1" t="n">
         <f aca="false">J7</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="61" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="C8" s="54" t="s">
         <v>72</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="E8" s="62" t="str">
         <f aca="false">COUNTIF(C8:C8,"✔")&amp;" / 1"</f>
         <v>1 / 1</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="H8" s="6" t="n">
+      <c r="G8" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="H8" s="1" t="n">
         <f aca="false">COUNTIF(C8:C8,"✔")</f>
         <v>1</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="1" t="n">
         <f aca="false">IF(H8=I8,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="1" t="n">
         <f aca="false">J8*K7</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="61" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="C9" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="E9" s="62" t="str">
         <f aca="false">COUNTIF(C9:C9,"✔")&amp;" / 1"</f>
         <v>1 / 1</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="H9" s="6" t="n">
+      <c r="G9" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <f aca="false">COUNTIF(C9:C9,"✔")</f>
         <v>1</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="1" t="n">
         <f aca="false">IF(H9=I9,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="1" t="n">
         <f aca="false">J9*K8</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="61" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="C10" s="54" t="s">
         <v>72</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="E10" s="62" t="str">
         <f aca="false">COUNTIF(C10:C10,"✔")&amp;" / 1"</f>
         <v>1 / 1</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="H10" s="6" t="n">
+      <c r="G10" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="H10" s="1" t="n">
         <f aca="false">COUNTIF(C10:C10,"✔")</f>
         <v>1</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="1" t="n">
         <f aca="false">IF(H10=I10,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="1" t="n">
         <f aca="false">J10*K9</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="61" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="C11" s="51"/>
       <c r="D11" s="52" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="E11" s="62" t="str">
         <f aca="false">COUNTIF(C11:C11,"✔")&amp;" / 1"</f>
         <v>0 / 1</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="1" t="n">
         <f aca="false">COUNTIF(C11:C11,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="1" t="n">
         <f aca="false">IF(H11=I11,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="1" t="n">
         <f aca="false">J11*K10</f>
         <v>0</v>
       </c>
@@ -4389,19 +4418,19 @@
   <dimension ref="B1:M16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="6" t="n">
+      <c r="M1" s="1" t="n">
         <f aca="false">SUM(H7:H11)</f>
         <v>5</v>
       </c>
@@ -4413,21 +4442,21 @@
       <c r="C2" s="57"/>
       <c r="D2" s="57"/>
       <c r="E2" s="63" t="s">
-        <v>355</v>
-      </c>
-      <c r="M2" s="6" t="n">
+        <v>365</v>
+      </c>
+      <c r="M2" s="1" t="n">
         <f aca="false">SUM(I7:I11)</f>
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="44" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="1" t="n">
         <f aca="false">SUM(K7:K11)</f>
         <v>2</v>
       </c>
@@ -4445,7 +4474,7 @@
       <c r="E4" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="1" t="n">
         <f aca="false">SUM(J7:J11)</f>
         <v>2</v>
       </c>
@@ -4464,7 +4493,7 @@
         <v>2 / 5</v>
       </c>
       <c r="E5" s="60" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4483,33 +4512,33 @@
     </row>
     <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="61" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C7" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="E7" s="53" t="str">
         <f aca="false">COUNTIF(C7:C8,"✔")&amp;" / 2"</f>
         <v>2 / 2</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H7" s="6" t="n">
+      <c r="G7" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H7" s="1" t="n">
         <f aca="false">COUNTIF(C7:C8,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="1" t="n">
         <f aca="false">IF(H7=I7,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="1" t="n">
         <f aca="false">J7</f>
         <v>1</v>
       </c>
@@ -4520,57 +4549,57 @@
         <v>72</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="E8" s="53"/>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="1" t="n">
         <f aca="false">COUNTIF(C9:C10,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="1" t="n">
         <f aca="false">IF(H8=I8,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="1" t="n">
         <f aca="false">J8*K7</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="61" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="C9" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="E9" s="53" t="str">
         <f aca="false">COUNTIF(C9:C10,"✔")&amp;" / 2"</f>
         <v>2 / 2</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="H9" s="6" t="n">
+      <c r="G9" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <f aca="false">COUNTIF(C11:C12,"✔")</f>
         <v>1</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="1" t="n">
         <f aca="false">IF(H9=I9,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="1" t="n">
         <f aca="false">J9*K8</f>
         <v>0</v>
       </c>
@@ -4581,57 +4610,57 @@
         <v>72</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="E10" s="53"/>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="1" t="n">
         <f aca="false">COUNTIF(C13:C14,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="1" t="n">
         <f aca="false">IF(H10=I10,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="1" t="n">
         <f aca="false">J10*K9</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="61" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="C11" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="E11" s="53" t="str">
         <f aca="false">COUNTIF(C11:C12,"✔")&amp;" / 2"</f>
         <v>1 / 2</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="H11" s="6" t="n">
+      <c r="G11" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="H11" s="1" t="n">
         <f aca="false">COUNTIF(C15:C16,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="1" t="n">
         <f aca="false">IF(H11=I11,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="1" t="n">
         <f aca="false">J11*K10</f>
         <v>0</v>
       </c>
@@ -4640,17 +4669,17 @@
       <c r="B12" s="61"/>
       <c r="C12" s="54"/>
       <c r="D12" s="55" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="E12" s="53"/>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="61" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="C13" s="51"/>
       <c r="D13" s="52" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="E13" s="53" t="str">
         <f aca="false">COUNTIF(C13:C14,"✔")&amp;" / 2"</f>
@@ -4661,17 +4690,17 @@
       <c r="B14" s="61"/>
       <c r="C14" s="54"/>
       <c r="D14" s="55" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="E14" s="53"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="61" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="C15" s="51"/>
       <c r="D15" s="52" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="E15" s="53" t="str">
         <f aca="false">COUNTIF(C15:C16,"✔")&amp;" / 2"</f>
@@ -4682,7 +4711,7 @@
       <c r="B16" s="61"/>
       <c r="C16" s="54"/>
       <c r="D16" s="55" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="E16" s="53"/>
     </row>
@@ -4759,19 +4788,19 @@
   <dimension ref="B1:M16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="6" t="n">
+      <c r="M1" s="1" t="n">
         <f aca="false">SUM(H7:H11)</f>
         <v>7</v>
       </c>
@@ -4783,21 +4812,21 @@
       <c r="C2" s="65"/>
       <c r="D2" s="65"/>
       <c r="E2" s="66" t="s">
-        <v>372</v>
-      </c>
-      <c r="M2" s="6" t="n">
+        <v>382</v>
+      </c>
+      <c r="M2" s="1" t="n">
         <f aca="false">SUM(I7:I11)</f>
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="44" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="1" t="n">
         <f aca="false">SUM(K7:K11)</f>
         <v>3</v>
       </c>
@@ -4815,7 +4844,7 @@
       <c r="E4" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="1" t="n">
         <f aca="false">SUM(J7:J11)</f>
         <v>3</v>
       </c>
@@ -4834,7 +4863,7 @@
         <v>3 / 5</v>
       </c>
       <c r="E5" s="69" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4853,33 +4882,33 @@
     </row>
     <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="70" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="C7" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="E7" s="53" t="str">
         <f aca="false">COUNTIF(C7:C8,"✔")&amp;" / 2"</f>
         <v>2 / 2</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="H7" s="6" t="n">
+      <c r="G7" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H7" s="1" t="n">
         <f aca="false">COUNTIF(C7:C8,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="1" t="n">
         <f aca="false">IF(H7=I7,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="1" t="n">
         <f aca="false">J7</f>
         <v>1</v>
       </c>
@@ -4890,57 +4919,57 @@
         <v>72</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="E8" s="53"/>
-      <c r="G8" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="H8" s="6" t="n">
+      <c r="G8" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="H8" s="1" t="n">
         <f aca="false">COUNTIF(C9:C10,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="1" t="n">
         <f aca="false">IF(H8=I8,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="1" t="n">
         <f aca="false">J8*K7</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="70" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="C9" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="E9" s="53" t="str">
         <f aca="false">COUNTIF(C9:C10,"✔")&amp;" / 2"</f>
         <v>2 / 2</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="H9" s="6" t="n">
+      <c r="G9" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <f aca="false">COUNTIF(C11:C12,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="1" t="n">
         <f aca="false">IF(H9=I9,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="1" t="n">
         <f aca="false">J9*K8</f>
         <v>1</v>
       </c>
@@ -4951,57 +4980,57 @@
         <v>72</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="E10" s="53"/>
-      <c r="G10" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="H10" s="6" t="n">
+      <c r="G10" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="H10" s="1" t="n">
         <f aca="false">COUNTIF(C13:C14,"✔")</f>
         <v>1</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="1" t="n">
         <f aca="false">IF(H10=I10,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="1" t="n">
         <f aca="false">J10*K9</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="70" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="C11" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="E11" s="53" t="str">
         <f aca="false">COUNTIF(C11:C12,"✔")&amp;" / 2"</f>
         <v>2 / 2</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="1" t="n">
         <f aca="false">COUNTIF(C15:C16,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="1" t="n">
         <f aca="false">IF(H11=I11,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="1" t="n">
         <f aca="false">J11*K10</f>
         <v>0</v>
       </c>
@@ -5012,19 +5041,19 @@
         <v>72</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="E12" s="53"/>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="70" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="C13" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="E13" s="53" t="str">
         <f aca="false">COUNTIF(C13:C14,"✔")&amp;" / 2"</f>
@@ -5035,17 +5064,17 @@
       <c r="B14" s="70"/>
       <c r="C14" s="54"/>
       <c r="D14" s="55" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="E14" s="53"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="70" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="C15" s="51"/>
       <c r="D15" s="52" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="E15" s="53" t="str">
         <f aca="false">COUNTIF(C15:C16,"✔")&amp;" / 2"</f>
@@ -5056,7 +5085,7 @@
       <c r="B16" s="70"/>
       <c r="C16" s="54"/>
       <c r="D16" s="55" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="E16" s="53"/>
     </row>
@@ -5133,19 +5162,19 @@
   <dimension ref="B1:M14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="71" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="6" t="n">
+      <c r="M1" s="1" t="n">
         <f aca="false">SUM(H7:H10)</f>
         <v>8</v>
       </c>
@@ -5157,21 +5186,21 @@
       <c r="C2" s="72"/>
       <c r="D2" s="72"/>
       <c r="E2" s="63" t="s">
-        <v>355</v>
-      </c>
-      <c r="M2" s="6" t="n">
+        <v>365</v>
+      </c>
+      <c r="M2" s="1" t="n">
         <f aca="false">SUM(I7:I10)</f>
         <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="44" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="1" t="n">
         <f aca="false">SUM(K7:K10)</f>
         <v>4</v>
       </c>
@@ -5189,7 +5218,7 @@
       <c r="E4" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="1" t="n">
         <f aca="false">SUM(J7:J10)</f>
         <v>4</v>
       </c>
@@ -5208,7 +5237,7 @@
         <v>4 / 4</v>
       </c>
       <c r="E5" s="75" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5227,33 +5256,33 @@
     </row>
     <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="76" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="C7" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="E7" s="53" t="str">
         <f aca="false">COUNTIF(C7:C8,"✔")&amp;" / 2"</f>
         <v>2 / 2</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="H7" s="6" t="n">
+      <c r="G7" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="H7" s="1" t="n">
         <f aca="false">COUNTIF(C7:C8,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="1" t="n">
         <f aca="false">IF(H7=I7,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="1" t="n">
         <f aca="false">J7</f>
         <v>1</v>
       </c>
@@ -5264,57 +5293,57 @@
         <v>72</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="E8" s="53"/>
-      <c r="G8" s="6" t="s">
-        <v>398</v>
-      </c>
-      <c r="H8" s="6" t="n">
+      <c r="G8" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="H8" s="1" t="n">
         <f aca="false">COUNTIF(C9:C10,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="1" t="n">
         <f aca="false">IF(H8=I8,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="1" t="n">
         <f aca="false">J8*K7</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="76" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="C9" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="E9" s="53" t="str">
         <f aca="false">COUNTIF(C9:C10,"✔")&amp;" / 2"</f>
         <v>2 / 2</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="H9" s="6" t="n">
+      <c r="G9" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <f aca="false">COUNTIF(C11:C12,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="1" t="n">
         <f aca="false">IF(H9=I9,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="1" t="n">
         <f aca="false">J9*K8</f>
         <v>1</v>
       </c>
@@ -5325,37 +5354,37 @@
         <v>72</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="E10" s="53"/>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="1" t="n">
         <f aca="false">COUNTIF(C13:C14,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="1" t="n">
         <f aca="false">IF(H10=I10,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="1" t="n">
         <f aca="false">J10*K9</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="76" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C11" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="E11" s="53" t="str">
         <f aca="false">COUNTIF(C11:C12,"✔")&amp;" / 2"</f>
@@ -5368,19 +5397,19 @@
         <v>72</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="E12" s="53"/>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="76" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="C13" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="E13" s="53" t="str">
         <f aca="false">COUNTIF(C13:C14,"✔")&amp;" / 2"</f>
@@ -5393,7 +5422,7 @@
         <v>72</v>
       </c>
       <c r="D14" s="55" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="E14" s="53"/>
     </row>
@@ -5463,19 +5492,19 @@
   <dimension ref="B1:M16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="6" t="n">
+      <c r="M1" s="1" t="n">
         <f aca="false">SUM(H7:H11)</f>
         <v>7</v>
       </c>
@@ -5489,19 +5518,19 @@
       <c r="E2" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="M2" s="1" t="n">
         <f aca="false">SUM(I7:I11)</f>
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="44" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="1" t="n">
         <f aca="false">SUM(K7:K11)</f>
         <v>3</v>
       </c>
@@ -5519,7 +5548,7 @@
       <c r="E4" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="1" t="n">
         <f aca="false">SUM(J7:J11)</f>
         <v>3</v>
       </c>
@@ -5538,7 +5567,7 @@
         <v>3 / 5</v>
       </c>
       <c r="E5" s="81" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5557,33 +5586,33 @@
     </row>
     <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="82" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="C7" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="E7" s="53" t="str">
         <f aca="false">COUNTIF(C7:C8,"✔")&amp;" / 2"</f>
         <v>2 / 2</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="H7" s="6" t="n">
+      <c r="G7" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="H7" s="1" t="n">
         <f aca="false">COUNTIF(C7:C8,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="1" t="n">
         <f aca="false">IF(H7=I7,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="1" t="n">
         <f aca="false">J7</f>
         <v>1</v>
       </c>
@@ -5594,57 +5623,57 @@
         <v>72</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="E8" s="53"/>
-      <c r="G8" s="6" t="s">
-        <v>414</v>
-      </c>
-      <c r="H8" s="6" t="n">
+      <c r="G8" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="H8" s="1" t="n">
         <f aca="false">COUNTIF(C9:C10,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="1" t="n">
         <f aca="false">IF(H8=I8,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="1" t="n">
         <f aca="false">J8*K7</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="82" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="C9" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="E9" s="53" t="str">
         <f aca="false">COUNTIF(C9:C10,"✔")&amp;" / 2"</f>
         <v>2 / 2</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>417</v>
-      </c>
-      <c r="H9" s="6" t="n">
+      <c r="G9" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <f aca="false">COUNTIF(C11:C12,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="1" t="n">
         <f aca="false">IF(H9=I9,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="1" t="n">
         <f aca="false">J9*K8</f>
         <v>1</v>
       </c>
@@ -5655,57 +5684,57 @@
         <v>72</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="E10" s="53"/>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="1" t="n">
         <f aca="false">COUNTIF(C13:C14,"✔")</f>
         <v>1</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="1" t="n">
         <f aca="false">IF(H10=I10,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="1" t="n">
         <f aca="false">J10*K9</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="82" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="C11" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="E11" s="53" t="str">
         <f aca="false">COUNTIF(C11:C12,"✔")&amp;" / 2"</f>
         <v>2 / 2</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="1" t="n">
         <f aca="false">COUNTIF(C15:C16,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="1" t="n">
         <f aca="false">IF(H11=I11,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="1" t="n">
         <f aca="false">J11*K10</f>
         <v>0</v>
       </c>
@@ -5716,19 +5745,19 @@
         <v>72</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="E12" s="53"/>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="82" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="C13" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="E13" s="53" t="str">
         <f aca="false">COUNTIF(C13:C14,"✔")&amp;" / 2"</f>
@@ -5739,17 +5768,17 @@
       <c r="B14" s="82"/>
       <c r="C14" s="54"/>
       <c r="D14" s="55" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="E14" s="53"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="82" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="C15" s="51"/>
       <c r="D15" s="52" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="E15" s="53" t="str">
         <f aca="false">COUNTIF(C15:C16,"✔")&amp;" / 2"</f>
@@ -5760,7 +5789,7 @@
       <c r="B16" s="82"/>
       <c r="C16" s="54"/>
       <c r="D16" s="55" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="E16" s="53"/>
     </row>
@@ -5837,8 +5866,8 @@
   <dimension ref="B2:H22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5853,15 +5882,15 @@
       <c r="H2" s="32"/>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="33" t="s">
@@ -5937,7 +5966,7 @@
       <c r="G13" s="36"/>
       <c r="H13" s="36"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="37" t="s">
         <v>59</v>
       </c>
@@ -5996,7 +6025,7 @@
       <c r="G21" s="42"/>
       <c r="H21" s="42"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="42"/>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
@@ -6038,19 +6067,19 @@
   <dimension ref="B1:M29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="6" t="n">
+      <c r="M1" s="1" t="n">
         <f aca="false">SUM(H7:H12)</f>
         <v>15</v>
       </c>
@@ -6064,7 +6093,7 @@
       <c r="E2" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="M2" s="1" t="n">
         <f aca="false">SUM(I7:I12)</f>
         <v>23</v>
       </c>
@@ -6076,7 +6105,7 @@
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="1" t="n">
         <f aca="false">SUM(K7:K12)</f>
         <v>3</v>
       </c>
@@ -6094,7 +6123,7 @@
       <c r="E4" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="1" t="n">
         <f aca="false">SUM(J7:J12)</f>
         <v>3</v>
       </c>
@@ -6144,21 +6173,21 @@
         <f aca="false">COUNTIF(C7:C9,"✔")&amp;" / 3"</f>
         <v>3 / 3</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="1" t="n">
         <f aca="false">COUNTIF(C7:C9,"✔")</f>
         <v>3</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="1" t="n">
         <f aca="false">IF(H7=I7,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="1" t="n">
         <f aca="false">J7</f>
         <v>1</v>
       </c>
@@ -6172,21 +6201,21 @@
         <v>78</v>
       </c>
       <c r="E8" s="53"/>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="1" t="n">
         <f aca="false">COUNTIF(C10:C14,"✔")</f>
         <v>5</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="1" t="n">
         <f aca="false">IF(H8=I8,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="1" t="n">
         <f aca="false">J8*K7</f>
         <v>1</v>
       </c>
@@ -6200,21 +6229,21 @@
         <v>80</v>
       </c>
       <c r="E9" s="53"/>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="1" t="n">
         <f aca="false">COUNTIF(C15:C19,"✔")</f>
         <v>5</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="1" t="n">
         <f aca="false">IF(H9=I9,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="1" t="n">
         <f aca="false">J9*K8</f>
         <v>1</v>
       </c>
@@ -6233,21 +6262,21 @@
         <f aca="false">COUNTIF(C10:C14,"✔")&amp;" / 5"</f>
         <v>5 / 5</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="1" t="n">
         <f aca="false">COUNTIF(C20:C24,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="1" t="n">
         <f aca="false">IF(H10=I10,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="1" t="n">
         <f aca="false">J10*K9</f>
         <v>0</v>
       </c>
@@ -6261,21 +6290,21 @@
         <v>85</v>
       </c>
       <c r="E11" s="53"/>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="1" t="n">
         <f aca="false">COUNTIF(C25:C27,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="1" t="n">
         <f aca="false">IF(H11=I11,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="1" t="n">
         <f aca="false">J11*K10</f>
         <v>0</v>
       </c>
@@ -6289,21 +6318,21 @@
         <v>87</v>
       </c>
       <c r="E12" s="53"/>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="1" t="n">
         <f aca="false">COUNTIF(C28:C29,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I12" s="0" t="n">
+      <c r="I12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="1" t="n">
         <f aca="false">IF(H12=I12,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="K12" s="1" t="n">
         <f aca="false">J12*K11</f>
         <v>0</v>
       </c>
@@ -6562,19 +6591,19 @@
   <dimension ref="B1:M25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="6" t="n">
+      <c r="M1" s="1" t="n">
         <f aca="false">SUM(H7:H12)</f>
         <v>15</v>
       </c>
@@ -6588,7 +6617,7 @@
       <c r="E2" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="M2" s="1" t="n">
         <f aca="false">SUM(I7:I12)</f>
         <v>19</v>
       </c>
@@ -6600,7 +6629,7 @@
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="1" t="n">
         <f aca="false">SUM(K7:K12)</f>
         <v>4</v>
       </c>
@@ -6618,7 +6647,7 @@
       <c r="E4" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="1" t="n">
         <f aca="false">SUM(J7:J12)</f>
         <v>4</v>
       </c>
@@ -6668,21 +6697,21 @@
         <f aca="false">COUNTIF(C7:C9,"✔")&amp;" / 3"</f>
         <v>3 / 3</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="1" t="n">
         <f aca="false">COUNTIF(C7:C9,"✔")</f>
         <v>3</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="1" t="n">
         <f aca="false">IF(H7=I7,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="1" t="n">
         <f aca="false">J7</f>
         <v>1</v>
       </c>
@@ -6696,21 +6725,21 @@
         <v>113</v>
       </c>
       <c r="E8" s="53"/>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="1" t="n">
         <f aca="false">COUNTIF(C10:C13,"✔")</f>
         <v>4</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="1" t="n">
         <f aca="false">IF(H8=I8,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="1" t="n">
         <f aca="false">J8*K7</f>
         <v>1</v>
       </c>
@@ -6724,21 +6753,21 @@
         <v>115</v>
       </c>
       <c r="E9" s="53"/>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="1" t="n">
         <f aca="false">COUNTIF(C14:C16,"✔")</f>
         <v>3</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="1" t="n">
         <f aca="false">IF(H9=I9,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="1" t="n">
         <f aca="false">J9*K8</f>
         <v>1</v>
       </c>
@@ -6757,21 +6786,21 @@
         <f aca="false">COUNTIF(C10:C13,"✔")&amp;" / 4"</f>
         <v>4 / 4</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="1" t="n">
         <f aca="false">COUNTIF(C17:C21,"✔")</f>
         <v>5</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="1" t="n">
         <f aca="false">IF(H10=I10,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="1" t="n">
         <f aca="false">J10*K9</f>
         <v>1</v>
       </c>
@@ -6785,21 +6814,21 @@
         <v>120</v>
       </c>
       <c r="E11" s="53"/>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="1" t="n">
         <f aca="false">COUNTIF(C22:C23,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="1" t="n">
         <f aca="false">IF(H11=I11,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="1" t="n">
         <f aca="false">J11*K10</f>
         <v>0</v>
       </c>
@@ -6813,21 +6842,21 @@
         <v>122</v>
       </c>
       <c r="E12" s="53"/>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="1" t="n">
         <f aca="false">COUNTIF(C24:C25,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I12" s="0" t="n">
+      <c r="I12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="1" t="n">
         <f aca="false">IF(H12=I12,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="K12" s="1" t="n">
         <f aca="false">J12*K11</f>
         <v>0</v>
       </c>
@@ -7054,19 +7083,19 @@
   <dimension ref="B1:M36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="6" t="n">
+      <c r="M1" s="1" t="n">
         <f aca="false">SUM(H7:H12)</f>
         <v>17</v>
       </c>
@@ -7080,7 +7109,7 @@
       <c r="E2" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="M2" s="1" t="n">
         <f aca="false">SUM(I7:I12)</f>
         <v>30</v>
       </c>
@@ -7092,7 +7121,7 @@
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="1" t="n">
         <f aca="false">SUM(K7:K12)</f>
         <v>2</v>
       </c>
@@ -7110,7 +7139,7 @@
       <c r="E4" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="1" t="n">
         <f aca="false">SUM(J7:J12)</f>
         <v>2</v>
       </c>
@@ -7160,21 +7189,21 @@
         <f aca="false">COUNTIF(C7:C10,"✔")&amp;" / 4"</f>
         <v>4 / 4</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="1" t="n">
         <f aca="false">COUNTIF(C7:C10,"✔")</f>
         <v>4</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="1" t="n">
         <f aca="false">IF(H7=I7,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="1" t="n">
         <f aca="false">J7</f>
         <v>1</v>
       </c>
@@ -7188,21 +7217,21 @@
         <v>145</v>
       </c>
       <c r="E8" s="53"/>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="1" t="n">
         <f aca="false">COUNTIF(C11:C19,"✔")</f>
         <v>9</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="1" t="n">
         <f aca="false">IF(H8=I8,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="1" t="n">
         <f aca="false">J8*K7</f>
         <v>1</v>
       </c>
@@ -7216,21 +7245,21 @@
         <v>147</v>
       </c>
       <c r="E9" s="53"/>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="1" t="n">
         <f aca="false">COUNTIF(C20:C26,"✔")</f>
         <v>4</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="1" t="n">
         <f aca="false">IF(H9=I9,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="1" t="n">
         <f aca="false">J9*K8</f>
         <v>0</v>
       </c>
@@ -7244,21 +7273,21 @@
         <v>149</v>
       </c>
       <c r="E10" s="53"/>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="1" t="n">
         <f aca="false">COUNTIF(C27:C30,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="1" t="n">
         <f aca="false">IF(H10=I10,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="1" t="n">
         <f aca="false">J10*K9</f>
         <v>0</v>
       </c>
@@ -7277,21 +7306,21 @@
         <f aca="false">COUNTIF(C11:C19,"✔")&amp;" / 9"</f>
         <v>9 / 9</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="1" t="n">
         <f aca="false">COUNTIF(C31:C33,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="1" t="n">
         <f aca="false">IF(H11=I11,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="1" t="n">
         <f aca="false">J11*K10</f>
         <v>0</v>
       </c>
@@ -7305,21 +7334,21 @@
         <v>153</v>
       </c>
       <c r="E12" s="53"/>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="1" t="n">
         <f aca="false">COUNTIF(C34:C36,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I12" s="0" t="n">
+      <c r="I12" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="1" t="n">
         <f aca="false">IF(H12=I12,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="K12" s="1" t="n">
         <f aca="false">J12*K11</f>
         <v>0</v>
       </c>
@@ -7635,24 +7664,24 @@
     <tabColor rgb="FFB07D12"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:M27"/>
+  <dimension ref="B1:M37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="6" t="n">
+      <c r="M1" s="1" t="n">
         <f aca="false">SUM(H7:H12)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7664,9 +7693,9 @@
       <c r="E2" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="M2" s="1" t="n">
         <f aca="false">SUM(I7:I12)</f>
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7676,9 +7705,9 @@
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="1" t="n">
         <f aca="false">SUM(K7:K12)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7694,23 +7723,23 @@
       <c r="E4" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="1" t="n">
         <f aca="false">SUM(J7:J12)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="46" t="str">
         <f aca="false">IF(M3=0,"Not started",INDEX(G7:G12,M3))</f>
-        <v>Architecture Selected</v>
+        <v>Not started</v>
       </c>
       <c r="C5" s="47" t="n">
         <f aca="false">IF(M2=0,0,M1/M2)</f>
-        <v>0.285714285714286</v>
+        <v>0</v>
       </c>
       <c r="D5" s="46" t="str">
         <f aca="false">M4&amp;" / "&amp;6</f>
-        <v>1 / 6</v>
+        <v>0 / 6</v>
       </c>
       <c r="E5" s="48" t="s">
         <v>141</v>
@@ -7734,176 +7763,159 @@
       <c r="B7" s="50" t="s">
         <v>182</v>
       </c>
-      <c r="C7" s="51" t="s">
-        <v>72</v>
-      </c>
+      <c r="C7" s="51"/>
       <c r="D7" s="52" t="s">
         <v>183</v>
       </c>
       <c r="E7" s="53" t="str">
-        <f aca="false">COUNTIF(C7:C10,"✔")&amp;" / 4"</f>
-        <v>4 / 4</v>
-      </c>
-      <c r="G7" s="6" t="s">
+        <f aca="false">COUNTIF(C7:C13,"✔")&amp;" / 7"</f>
+        <v>0 / 7</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="H7" s="6" t="n">
-        <f aca="false">COUNTIF(C7:C10,"✔")</f>
-        <v>4</v>
-      </c>
-      <c r="I7" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" s="6" t="n">
+      <c r="H7" s="1" t="n">
+        <f aca="false">COUNTIF(C7:C13,"✔")</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" s="1" t="n">
         <f aca="false">IF(H7=I7,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="K7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="n">
         <f aca="false">J7</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="50"/>
-      <c r="C8" s="54" t="s">
-        <v>72</v>
-      </c>
+      <c r="C8" s="54"/>
       <c r="D8" s="55" t="s">
         <v>185</v>
       </c>
       <c r="E8" s="53"/>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="H8" s="6" t="n">
-        <f aca="false">COUNTIF(C11:C14,"✔")</f>
-        <v>2</v>
-      </c>
-      <c r="I8" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" s="6" t="n">
+      <c r="H8" s="1" t="n">
+        <f aca="false">COUNTIF(C14:C19,"✔")</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" s="1" t="n">
         <f aca="false">IF(H8=I8,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="1" t="n">
         <f aca="false">J8*K7</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="50"/>
-      <c r="C9" s="51" t="s">
-        <v>72</v>
-      </c>
+      <c r="C9" s="51"/>
       <c r="D9" s="52" t="s">
         <v>187</v>
       </c>
       <c r="E9" s="53"/>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H9" s="6" t="n">
-        <f aca="false">COUNTIF(C15:C18,"✔")</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" s="6" t="n">
+      <c r="H9" s="1" t="n">
+        <f aca="false">COUNTIF(C20:C26,"✔")</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" s="1" t="n">
         <f aca="false">IF(H9=I9,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="1" t="n">
         <f aca="false">J9*K8</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="50"/>
-      <c r="C10" s="54" t="s">
-        <v>72</v>
-      </c>
+      <c r="C10" s="54"/>
       <c r="D10" s="55" t="s">
         <v>189</v>
       </c>
       <c r="E10" s="53"/>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="H10" s="6" t="n">
-        <f aca="false">COUNTIF(C19:C22,"✔")</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="0" t="n">
+      <c r="H10" s="1" t="n">
+        <f aca="false">COUNTIF(C27:C30,"✔")</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="1" t="n">
         <f aca="false">IF(H10=I10,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="1" t="n">
         <f aca="false">J10*K9</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="50"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="52" t="s">
         <v>191</v>
       </c>
-      <c r="C11" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="52" t="s">
-        <v>192</v>
-      </c>
-      <c r="E11" s="53" t="str">
-        <f aca="false">COUNTIF(C11:C14,"✔")&amp;" / 4"</f>
-        <v>2 / 4</v>
-      </c>
-      <c r="G11" s="6" t="s">
+      <c r="E11" s="53"/>
+      <c r="G11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="6" t="n">
-        <f aca="false">COUNTIF(C23:C25,"✔")</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="0" t="n">
+      <c r="H11" s="1" t="n">
+        <f aca="false">COUNTIF(C31:C33,"✔")</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="1" t="n">
         <f aca="false">IF(H11=I11,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="1" t="n">
         <f aca="false">J11*K10</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="50"/>
-      <c r="C12" s="54" t="s">
-        <v>72</v>
-      </c>
+      <c r="C12" s="54"/>
       <c r="D12" s="55" t="s">
+        <v>192</v>
+      </c>
+      <c r="E12" s="53"/>
+      <c r="G12" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E12" s="53"/>
-      <c r="G12" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <f aca="false">COUNTIF(C26:C27,"✔")</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="6" t="n">
+      <c r="H12" s="1" t="n">
+        <f aca="false">COUNTIF(C34:C37,"✔")</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" s="1" t="n">
         <f aca="false">IF(H12=I12,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="K12" s="1" t="n">
         <f aca="false">J12*K11</f>
         <v>0</v>
       </c>
@@ -7912,36 +7924,36 @@
       <c r="B13" s="50"/>
       <c r="C13" s="51"/>
       <c r="D13" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="E13" s="53"/>
+    </row>
+    <row r="14" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="50" t="s">
         <v>195</v>
       </c>
-      <c r="E13" s="53"/>
-    </row>
-    <row r="14" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="50"/>
       <c r="C14" s="54"/>
       <c r="D14" s="55" t="s">
         <v>196</v>
       </c>
-      <c r="E14" s="53"/>
+      <c r="E14" s="53" t="str">
+        <f aca="false">COUNTIF(C14:C19,"✔")&amp;" / 6"</f>
+        <v>0 / 6</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="50" t="s">
-        <v>197</v>
-      </c>
+      <c r="B15" s="50"/>
       <c r="C15" s="51"/>
       <c r="D15" s="52" t="s">
-        <v>198</v>
-      </c>
-      <c r="E15" s="53" t="str">
-        <f aca="false">COUNTIF(C15:C18,"✔")&amp;" / 4"</f>
-        <v>0 / 4</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="E15" s="53"/>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="50"/>
       <c r="C16" s="54"/>
       <c r="D16" s="55" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E16" s="53"/>
     </row>
@@ -7949,7 +7961,7 @@
       <c r="B17" s="50"/>
       <c r="C17" s="51"/>
       <c r="D17" s="52" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E17" s="53"/>
     </row>
@@ -7957,36 +7969,36 @@
       <c r="B18" s="50"/>
       <c r="C18" s="54"/>
       <c r="D18" s="55" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E18" s="53"/>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="50" t="s">
-        <v>202</v>
-      </c>
+      <c r="B19" s="50"/>
       <c r="C19" s="51"/>
       <c r="D19" s="52" t="s">
-        <v>203</v>
-      </c>
-      <c r="E19" s="53" t="str">
-        <f aca="false">COUNTIF(C19:C22,"✔")&amp;" / 4"</f>
-        <v>0 / 4</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="E19" s="53"/>
     </row>
     <row r="20" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="50"/>
+      <c r="B20" s="50" t="s">
+        <v>202</v>
+      </c>
       <c r="C20" s="54"/>
       <c r="D20" s="55" t="s">
-        <v>204</v>
-      </c>
-      <c r="E20" s="53"/>
+        <v>203</v>
+      </c>
+      <c r="E20" s="53" t="str">
+        <f aca="false">COUNTIF(C20:C26,"✔")&amp;" / 7"</f>
+        <v>0 / 7</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="50"/>
       <c r="C21" s="51"/>
       <c r="D21" s="52" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E21" s="53"/>
     </row>
@@ -7994,28 +8006,23 @@
       <c r="B22" s="50"/>
       <c r="C22" s="54"/>
       <c r="D22" s="55" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E22" s="53"/>
     </row>
     <row r="23" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="50" t="s">
-        <v>207</v>
-      </c>
+      <c r="B23" s="50"/>
       <c r="C23" s="51"/>
       <c r="D23" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="E23" s="53" t="str">
-        <f aca="false">COUNTIF(C23:C25,"✔")&amp;" / 3"</f>
-        <v>0 / 3</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="E23" s="53"/>
     </row>
     <row r="24" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="50"/>
       <c r="C24" s="54"/>
       <c r="D24" s="55" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E24" s="53"/>
     </row>
@@ -8023,47 +8030,137 @@
       <c r="B25" s="50"/>
       <c r="C25" s="51"/>
       <c r="D25" s="52" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E25" s="53"/>
     </row>
     <row r="26" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="50" t="s">
-        <v>211</v>
-      </c>
+      <c r="B26" s="50"/>
       <c r="C26" s="54"/>
       <c r="D26" s="55" t="s">
-        <v>212</v>
-      </c>
-      <c r="E26" s="53" t="str">
-        <f aca="false">COUNTIF(C26:C27,"✔")&amp;" / 2"</f>
-        <v>0 / 2</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="E26" s="53"/>
     </row>
     <row r="27" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="50"/>
+      <c r="B27" s="50" t="s">
+        <v>210</v>
+      </c>
       <c r="C27" s="51"/>
       <c r="D27" s="52" t="s">
+        <v>211</v>
+      </c>
+      <c r="E27" s="53" t="str">
+        <f aca="false">COUNTIF(C27:C30,"✔")&amp;" / 4"</f>
+        <v>0 / 4</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="50"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="55" t="s">
+        <v>212</v>
+      </c>
+      <c r="E28" s="53"/>
+    </row>
+    <row r="29" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="50"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="52" t="s">
         <v>213</v>
       </c>
-      <c r="E27" s="53"/>
+      <c r="E29" s="53"/>
+    </row>
+    <row r="30" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="50"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="E30" s="53"/>
+    </row>
+    <row r="31" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="C31" s="51"/>
+      <c r="D31" s="52" t="s">
+        <v>216</v>
+      </c>
+      <c r="E31" s="53" t="str">
+        <f aca="false">COUNTIF(C31:C33,"✔")&amp;" / 3"</f>
+        <v>0 / 3</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="50"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="55" t="s">
+        <v>217</v>
+      </c>
+      <c r="E32" s="53"/>
+    </row>
+    <row r="33" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="50"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="52" t="s">
+        <v>218</v>
+      </c>
+      <c r="E33" s="53"/>
+    </row>
+    <row r="34" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="C34" s="54"/>
+      <c r="D34" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="E34" s="53" t="str">
+        <f aca="false">COUNTIF(C34:C37,"✔")&amp;" / 4"</f>
+        <v>0 / 4</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="50"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="52" t="s">
+        <v>221</v>
+      </c>
+      <c r="E35" s="53"/>
+    </row>
+    <row r="36" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="50"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="55" t="s">
+        <v>222</v>
+      </c>
+      <c r="E36" s="53"/>
+    </row>
+    <row r="37" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="50"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="52" t="s">
+        <v>223</v>
+      </c>
+      <c r="E37" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="E7:E10"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="E11:E14"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="E15:E18"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="E19:E22"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="B7:B13"/>
+    <mergeCell ref="E7:E13"/>
+    <mergeCell ref="B14:B19"/>
+    <mergeCell ref="E14:E19"/>
+    <mergeCell ref="B20:B26"/>
+    <mergeCell ref="E20:E26"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="E27:E30"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="E34:E37"/>
   </mergeCells>
   <conditionalFormatting sqref="E7:E10">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
@@ -8128,19 +8225,19 @@
   <dimension ref="B1:M25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="6" t="n">
+      <c r="M1" s="1" t="n">
         <f aca="false">SUM(H7:H12)</f>
         <v>11</v>
       </c>
@@ -8154,19 +8251,19 @@
       <c r="E2" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="M2" s="1" t="n">
         <f aca="false">SUM(I7:I12)</f>
         <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="44" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="1" t="n">
         <f aca="false">SUM(K7:K12)</f>
         <v>2</v>
       </c>
@@ -8184,7 +8281,7 @@
       <c r="E4" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="1" t="n">
         <f aca="false">SUM(J7:J12)</f>
         <v>2</v>
       </c>
@@ -8203,7 +8300,7 @@
         <v>2 / 6</v>
       </c>
       <c r="E5" s="48" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8222,33 +8319,33 @@
     </row>
     <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="50" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="C7" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="E7" s="53" t="str">
         <f aca="false">COUNTIF(C7:C10,"✔")&amp;" / 4"</f>
         <v>4 / 4</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="H7" s="6" t="n">
+      <c r="G7" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H7" s="1" t="n">
         <f aca="false">COUNTIF(C7:C10,"✔")</f>
         <v>4</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="1" t="n">
         <f aca="false">IF(H7=I7,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="1" t="n">
         <f aca="false">J7</f>
         <v>1</v>
       </c>
@@ -8259,24 +8356,24 @@
         <v>72</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="E8" s="53"/>
-      <c r="G8" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="H8" s="6" t="n">
+      <c r="G8" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H8" s="1" t="n">
         <f aca="false">COUNTIF(C11:C15,"✔")</f>
         <v>5</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="1" t="n">
         <f aca="false">IF(H8=I8,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="1" t="n">
         <f aca="false">J8*K7</f>
         <v>1</v>
       </c>
@@ -8287,24 +8384,24 @@
         <v>72</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E9" s="53"/>
-      <c r="G9" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="H9" s="6" t="n">
+      <c r="G9" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <f aca="false">COUNTIF(C16:C18,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="1" t="n">
         <f aca="false">IF(H9=I9,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="1" t="n">
         <f aca="false">J9*K8</f>
         <v>0</v>
       </c>
@@ -8315,57 +8412,57 @@
         <v>72</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="E10" s="53"/>
-      <c r="G10" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="H10" s="6" t="n">
+      <c r="G10" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="H10" s="1" t="n">
         <f aca="false">COUNTIF(C19:C21,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="1" t="n">
         <f aca="false">IF(H10=I10,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="1" t="n">
         <f aca="false">J10*K9</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="50" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="C11" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="E11" s="53" t="str">
         <f aca="false">COUNTIF(C11:C15,"✔")&amp;" / 5"</f>
         <v>5 / 5</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="H11" s="6" t="n">
+      <c r="G11" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H11" s="1" t="n">
         <f aca="false">COUNTIF(C22:C23,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="1" t="n">
         <f aca="false">IF(H11=I11,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="1" t="n">
         <f aca="false">J11*K10</f>
         <v>0</v>
       </c>
@@ -8376,24 +8473,24 @@
         <v>72</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="E12" s="53"/>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="1" t="n">
         <f aca="false">COUNTIF(C24:C25,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I12" s="0" t="n">
+      <c r="I12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="1" t="n">
         <f aca="false">IF(H12=I12,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="K12" s="1" t="n">
         <f aca="false">J12*K11</f>
         <v>0</v>
       </c>
@@ -8404,7 +8501,7 @@
         <v>72</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="E13" s="53"/>
     </row>
@@ -8414,7 +8511,7 @@
         <v>72</v>
       </c>
       <c r="D14" s="55" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E14" s="53"/>
     </row>
@@ -8424,19 +8521,19 @@
         <v>72</v>
       </c>
       <c r="D15" s="52" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="E15" s="53"/>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="50" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="C16" s="54" t="s">
         <v>72</v>
       </c>
       <c r="D16" s="55" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="E16" s="53" t="str">
         <f aca="false">COUNTIF(C16:C18,"✔")&amp;" / 3"</f>
@@ -8449,7 +8546,7 @@
         <v>72</v>
       </c>
       <c r="D17" s="52" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E17" s="53"/>
     </row>
@@ -8457,17 +8554,17 @@
       <c r="B18" s="50"/>
       <c r="C18" s="54"/>
       <c r="D18" s="55" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E18" s="53"/>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="50" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C19" s="51"/>
       <c r="D19" s="52" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="E19" s="53" t="str">
         <f aca="false">COUNTIF(C19:C21,"✔")&amp;" / 3"</f>
@@ -8478,7 +8575,7 @@
       <c r="B20" s="50"/>
       <c r="C20" s="54"/>
       <c r="D20" s="55" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="E20" s="53"/>
     </row>
@@ -8486,17 +8583,17 @@
       <c r="B21" s="50"/>
       <c r="C21" s="51"/>
       <c r="D21" s="52" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="E21" s="53"/>
     </row>
     <row r="22" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="50" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C22" s="54"/>
       <c r="D22" s="55" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="E22" s="53" t="str">
         <f aca="false">COUNTIF(C22:C23,"✔")&amp;" / 2"</f>
@@ -8507,17 +8604,17 @@
       <c r="B23" s="50"/>
       <c r="C23" s="51"/>
       <c r="D23" s="52" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="E23" s="53"/>
     </row>
     <row r="24" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="50" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C24" s="54"/>
       <c r="D24" s="55" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="E24" s="53" t="str">
         <f aca="false">COUNTIF(C24:C25,"✔")&amp;" / 2"</f>
@@ -8528,7 +8625,7 @@
       <c r="B25" s="50"/>
       <c r="C25" s="51"/>
       <c r="D25" s="52" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="E25" s="53"/>
     </row>
@@ -8612,19 +8709,19 @@
   <dimension ref="B1:M23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="6" t="n">
+      <c r="M1" s="1" t="n">
         <f aca="false">SUM(H7:H11)</f>
         <v>11</v>
       </c>
@@ -8638,19 +8735,19 @@
       <c r="E2" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="M2" s="1" t="n">
         <f aca="false">SUM(I7:I11)</f>
         <v>17</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="44" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="1" t="n">
         <f aca="false">SUM(K7:K11)</f>
         <v>2</v>
       </c>
@@ -8668,7 +8765,7 @@
       <c r="E4" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="1" t="n">
         <f aca="false">SUM(J7:J11)</f>
         <v>2</v>
       </c>
@@ -8687,7 +8784,7 @@
         <v>2 / 5</v>
       </c>
       <c r="E5" s="48" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8706,33 +8803,33 @@
     </row>
     <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="50" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C7" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="E7" s="53" t="str">
         <f aca="false">COUNTIF(C7:C11,"✔")&amp;" / 5"</f>
         <v>5 / 5</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H7" s="6" t="n">
+      <c r="G7" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H7" s="1" t="n">
         <f aca="false">COUNTIF(C7:C11,"✔")</f>
         <v>5</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="1" t="n">
         <f aca="false">IF(H7=I7,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="1" t="n">
         <f aca="false">J7</f>
         <v>1</v>
       </c>
@@ -8743,24 +8840,24 @@
         <v>72</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E8" s="53"/>
-      <c r="G8" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="H8" s="6" t="n">
+      <c r="G8" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="H8" s="1" t="n">
         <f aca="false">COUNTIF(C12:C15,"✔")</f>
         <v>4</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="1" t="n">
         <f aca="false">IF(H8=I8,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="1" t="n">
         <f aca="false">J8*K7</f>
         <v>1</v>
       </c>
@@ -8771,24 +8868,24 @@
         <v>72</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="E9" s="53"/>
-      <c r="G9" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="H9" s="6" t="n">
+      <c r="G9" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <f aca="false">COUNTIF(C16:C18,"✔")</f>
         <v>2</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="1" t="n">
         <f aca="false">IF(H9=I9,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="1" t="n">
         <f aca="false">J9*K8</f>
         <v>0</v>
       </c>
@@ -8799,24 +8896,24 @@
         <v>72</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="E10" s="53"/>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="1" t="n">
         <f aca="false">COUNTIF(C19:C21,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="1" t="n">
         <f aca="false">IF(H10=I10,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="1" t="n">
         <f aca="false">J10*K9</f>
         <v>0</v>
       </c>
@@ -8827,37 +8924,37 @@
         <v>72</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="E11" s="53"/>
-      <c r="G11" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="H11" s="6" t="n">
+      <c r="G11" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="H11" s="1" t="n">
         <f aca="false">COUNTIF(C22:C23,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="1" t="n">
         <f aca="false">IF(H11=I11,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="1" t="n">
         <f aca="false">J11*K10</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="50" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="C12" s="54" t="s">
         <v>72</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="E12" s="53" t="str">
         <f aca="false">COUNTIF(C12:C15,"✔")&amp;" / 4"</f>
@@ -8870,7 +8967,7 @@
         <v>72</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="E13" s="53"/>
     </row>
@@ -8880,7 +8977,7 @@
         <v>72</v>
       </c>
       <c r="D14" s="55" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="E14" s="53"/>
     </row>
@@ -8890,19 +8987,19 @@
         <v>72</v>
       </c>
       <c r="D15" s="52" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E15" s="53"/>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="50" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="C16" s="54" t="s">
         <v>72</v>
       </c>
       <c r="D16" s="55" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="E16" s="53" t="str">
         <f aca="false">COUNTIF(C16:C18,"✔")&amp;" / 3"</f>
@@ -8915,7 +9012,7 @@
         <v>72</v>
       </c>
       <c r="D17" s="52" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="E17" s="53"/>
     </row>
@@ -8923,17 +9020,17 @@
       <c r="B18" s="50"/>
       <c r="C18" s="54"/>
       <c r="D18" s="55" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="E18" s="53"/>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="50" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="C19" s="51"/>
       <c r="D19" s="52" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="E19" s="53" t="str">
         <f aca="false">COUNTIF(C19:C21,"✔")&amp;" / 3"</f>
@@ -8944,7 +9041,7 @@
       <c r="B20" s="50"/>
       <c r="C20" s="54"/>
       <c r="D20" s="55" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="E20" s="53"/>
     </row>
@@ -8952,17 +9049,17 @@
       <c r="B21" s="50"/>
       <c r="C21" s="51"/>
       <c r="D21" s="52" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="E21" s="53"/>
     </row>
     <row r="22" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="50" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C22" s="54"/>
       <c r="D22" s="55" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="E22" s="53" t="str">
         <f aca="false">COUNTIF(C22:C23,"✔")&amp;" / 2"</f>
@@ -8973,7 +9070,7 @@
       <c r="B23" s="50"/>
       <c r="C23" s="51"/>
       <c r="D23" s="52" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="E23" s="53"/>
     </row>
@@ -9050,19 +9147,19 @@
   <dimension ref="B1:M23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="7" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="6" t="n">
+      <c r="M1" s="1" t="n">
         <f aca="false">SUM(H7:H12)</f>
         <v>7</v>
       </c>
@@ -9076,19 +9173,19 @@
       <c r="E2" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="M2" s="1" t="n">
         <f aca="false">SUM(I7:I12)</f>
         <v>17</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="44" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="1" t="n">
         <f aca="false">SUM(K7:K12)</f>
         <v>2</v>
       </c>
@@ -9106,7 +9203,7 @@
       <c r="E4" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="1" t="n">
         <f aca="false">SUM(J7:J12)</f>
         <v>2</v>
       </c>
@@ -9125,7 +9222,7 @@
         <v>2 / 6</v>
       </c>
       <c r="E5" s="48" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9144,33 +9241,33 @@
     </row>
     <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="50" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="C7" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="E7" s="53" t="str">
         <f aca="false">COUNTIF(C7:C9,"✔")&amp;" / 3"</f>
         <v>3 / 3</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="H7" s="6" t="n">
+      <c r="G7" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H7" s="1" t="n">
         <f aca="false">COUNTIF(C7:C9,"✔")</f>
         <v>3</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="1" t="n">
         <f aca="false">IF(H7=I7,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="1" t="n">
         <f aca="false">J7</f>
         <v>1</v>
       </c>
@@ -9181,24 +9278,24 @@
         <v>72</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="E8" s="53"/>
-      <c r="G8" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="H8" s="6" t="n">
+      <c r="G8" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="H8" s="1" t="n">
         <f aca="false">COUNTIF(C10:C12,"✔")</f>
         <v>3</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="1" t="n">
         <f aca="false">IF(H8=I8,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="1" t="n">
         <f aca="false">J8*K7</f>
         <v>1</v>
       </c>
@@ -9209,57 +9306,57 @@
         <v>72</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="E9" s="53"/>
-      <c r="G9" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="H9" s="6" t="n">
+      <c r="G9" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <f aca="false">COUNTIF(C13:C15,"✔")</f>
         <v>1</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="1" t="n">
         <f aca="false">IF(H9=I9,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="1" t="n">
         <f aca="false">J9*K8</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="50" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="C10" s="54" t="s">
         <v>72</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="E10" s="53" t="str">
         <f aca="false">COUNTIF(C10:C12,"✔")&amp;" / 3"</f>
         <v>3 / 3</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="H10" s="6" t="n">
+      <c r="G10" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H10" s="1" t="n">
         <f aca="false">COUNTIF(C16:C18,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="1" t="n">
         <f aca="false">IF(H10=I10,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="1" t="n">
         <f aca="false">J10*K9</f>
         <v>0</v>
       </c>
@@ -9270,24 +9367,24 @@
         <v>72</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="E11" s="53"/>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="1" t="n">
         <f aca="false">COUNTIF(C19:C21,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="1" t="n">
         <f aca="false">IF(H11=I11,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="1" t="n">
         <f aca="false">J11*K10</f>
         <v>0</v>
       </c>
@@ -9298,37 +9395,37 @@
         <v>72</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="E12" s="53"/>
-      <c r="G12" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="H12" s="6" t="n">
+      <c r="G12" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H12" s="1" t="n">
         <f aca="false">COUNTIF(C22:C23,"✔")</f>
         <v>0</v>
       </c>
-      <c r="I12" s="0" t="n">
+      <c r="I12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="1" t="n">
         <f aca="false">IF(H12=I12,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="K12" s="1" t="n">
         <f aca="false">J12*K11</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="50" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="C13" s="51" t="s">
         <v>72</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="E13" s="53" t="str">
         <f aca="false">COUNTIF(C13:C15,"✔")&amp;" / 3"</f>
@@ -9339,7 +9436,7 @@
       <c r="B14" s="50"/>
       <c r="C14" s="54"/>
       <c r="D14" s="55" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="E14" s="53"/>
     </row>
@@ -9347,17 +9444,17 @@
       <c r="B15" s="50"/>
       <c r="C15" s="51"/>
       <c r="D15" s="52" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="E15" s="53"/>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="50" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="C16" s="54"/>
       <c r="D16" s="55" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="E16" s="53" t="str">
         <f aca="false">COUNTIF(C16:C18,"✔")&amp;" / 3"</f>
@@ -9368,7 +9465,7 @@
       <c r="B17" s="50"/>
       <c r="C17" s="51"/>
       <c r="D17" s="52" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="E17" s="53"/>
     </row>
@@ -9376,17 +9473,17 @@
       <c r="B18" s="50"/>
       <c r="C18" s="54"/>
       <c r="D18" s="55" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="E18" s="53"/>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="50" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="C19" s="51"/>
       <c r="D19" s="52" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="E19" s="53" t="str">
         <f aca="false">COUNTIF(C19:C21,"✔")&amp;" / 3"</f>
@@ -9397,7 +9494,7 @@
       <c r="B20" s="50"/>
       <c r="C20" s="54"/>
       <c r="D20" s="55" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="E20" s="53"/>
     </row>
@@ -9405,17 +9502,17 @@
       <c r="B21" s="50"/>
       <c r="C21" s="51"/>
       <c r="D21" s="52" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="E21" s="53"/>
     </row>
     <row r="22" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="50" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C22" s="54"/>
       <c r="D22" s="55" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="E22" s="53" t="str">
         <f aca="false">COUNTIF(C22:C23,"✔")&amp;" / 2"</f>
@@ -9426,7 +9523,7 @@
       <c r="B23" s="50"/>
       <c r="C23" s="51"/>
       <c r="D23" s="52" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="E23" s="53"/>
     </row>

--- a/essence/EA_Alpha_Assessment.xlsx
+++ b/essence/EA_Alpha_Assessment.xlsx
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G12" s="107" t="inlineStr">
         <is>
-          <t>Pervasive</t>
+          <t>Evoluerend</t>
         </is>
       </c>
       <c r="H12" s="108">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="G20" s="107" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Effectief</t>
         </is>
       </c>
       <c r="H20" s="108">
@@ -2751,7 +2751,7 @@
     <row r="7" ht="35" customHeight="1" s="86">
       <c r="B7" s="157" t="inlineStr">
         <is>
-          <t>1. Initiated</t>
+          <t>1. Opgericht</t>
         </is>
       </c>
       <c r="C7" s="240" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="G7" s="85" t="inlineStr">
         <is>
-          <t>Initiated</t>
+          <t>Opgericht</t>
         </is>
       </c>
       <c r="H7" s="85">
@@ -2804,7 +2804,7 @@
       <c r="E8" s="161" t="n"/>
       <c r="G8" s="85" t="inlineStr">
         <is>
-          <t>Engaged</t>
+          <t>Actief</t>
         </is>
       </c>
       <c r="H8" s="85">
@@ -2826,7 +2826,7 @@
     <row r="9" ht="35" customHeight="1" s="86">
       <c r="B9" s="195" t="inlineStr">
         <is>
-          <t>2. Engaged</t>
+          <t>2. Actief</t>
         </is>
       </c>
       <c r="C9" s="235" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="G9" s="85" t="inlineStr">
         <is>
-          <t>Guiding</t>
+          <t>Sturend</t>
         </is>
       </c>
       <c r="H9" s="85">
@@ -2879,7 +2879,7 @@
       <c r="E10" s="161" t="n"/>
       <c r="G10" s="85" t="inlineStr">
         <is>
-          <t>Assured</t>
+          <t>Geborgd</t>
         </is>
       </c>
       <c r="H10" s="85">
@@ -2901,7 +2901,7 @@
     <row r="11" ht="35" customHeight="1" s="86">
       <c r="B11" s="157" t="inlineStr">
         <is>
-          <t>3. Guiding</t>
+          <t>3. Sturend</t>
         </is>
       </c>
       <c r="C11" s="240" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="G11" s="85" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Effectief</t>
         </is>
       </c>
       <c r="H11" s="85">
@@ -2956,7 +2956,7 @@
     <row r="13" ht="35" customHeight="1" s="86">
       <c r="B13" s="195" t="inlineStr">
         <is>
-          <t>4. Assured</t>
+          <t>4. Geborgd</t>
         </is>
       </c>
       <c r="C13" s="235" t="inlineStr">
@@ -2987,7 +2987,7 @@
     <row r="15" ht="35" customHeight="1" s="86">
       <c r="B15" s="157" t="inlineStr">
         <is>
-          <t>5. Effective</t>
+          <t>5. Effectief</t>
         </is>
       </c>
       <c r="C15" s="240" t="n"/>
@@ -4349,7 +4349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:M16"/>
+  <dimension ref="B1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="85" min="1" max="1"/>
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="M1" s="85">
-        <f>SUM(H7:H11)</f>
+        <f>SUM(H7:H9)</f>
         <v/>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
         </is>
       </c>
       <c r="M2" s="85">
-        <f>SUM(I7:I11)</f>
+        <f>SUM(I7:I9)</f>
         <v/>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="M3" s="85">
-        <f>SUM(K7:K11)</f>
+        <f>SUM(K7:K9)</f>
         <v/>
       </c>
     </row>
@@ -4420,13 +4420,13 @@
         </is>
       </c>
       <c r="M4" s="85">
-        <f>SUM(J7:J11)</f>
+        <f>SUM(J7:J9)</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="25.5" customHeight="1" s="86">
       <c r="B5" s="182">
-        <f>IF(M3=0,"Not started",INDEX(G7:G11,M3))</f>
+        <f>IF(M3=0,"Not started",INDEX(G7:G9,M3))</f>
         <v/>
       </c>
       <c r="C5" s="183">
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="D5" s="182">
-        <f>M4&amp;" / "&amp;5</f>
+        <f>M4&amp;" / "&amp;3</f>
         <v/>
       </c>
       <c r="E5" s="184" t="inlineStr">
@@ -4468,7 +4468,7 @@
     <row r="7" ht="35" customHeight="1" s="86">
       <c r="B7" s="127" t="inlineStr">
         <is>
-          <t>1. Seeded</t>
+          <t>1. Vastgesteld</t>
         </is>
       </c>
       <c r="C7" s="233" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="D7" s="220" t="inlineStr">
         <is>
-          <t>De behoefte aan een paved road wordt onderkend.</t>
+          <t>Een coherent service-chassis van goedgekeurde producten, patronen en standaarden is gepubliceerd.</t>
         </is>
       </c>
       <c r="E7" s="130">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="G7" s="85" t="inlineStr">
         <is>
-          <t>Seeded</t>
+          <t>Vastgesteld</t>
         </is>
       </c>
       <c r="H7" s="85">
@@ -4515,13 +4515,13 @@
       </c>
       <c r="D8" s="208" t="inlineStr">
         <is>
-          <t>Een eerste goedgekeurde standaardkeuze of twee bestaat al.</t>
+          <t>De goedgekeurde route is zelfbedienbaar.</t>
         </is>
       </c>
       <c r="E8" s="131" t="n"/>
       <c r="G8" s="85" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Toegepast</t>
         </is>
       </c>
       <c r="H8" s="85">
@@ -4543,7 +4543,7 @@
     <row r="9" ht="35" customHeight="1" s="86">
       <c r="B9" s="185" t="inlineStr">
         <is>
-          <t>2. Established</t>
+          <t>2. Toegepast</t>
         </is>
       </c>
       <c r="C9" s="235" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="D9" s="223" t="inlineStr">
         <is>
-          <t>Een samenhangend service-chassis van goedgekeurde producten, patronen en standaarden is gepubliceerd.</t>
+          <t>Teams bouwen standaard op de goedgekeurde route.</t>
         </is>
       </c>
       <c r="E9" s="188">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="G9" s="85" t="inlineStr">
         <is>
-          <t>Adopted</t>
+          <t>Evoluerend</t>
         </is>
       </c>
       <c r="H9" s="85">
@@ -4583,158 +4583,62 @@
     </row>
     <row r="10" ht="35" customHeight="1" s="86">
       <c r="B10" s="131" t="n"/>
-      <c r="C10" s="236" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
+      <c r="C10" s="236" t="n"/>
       <c r="D10" s="210" t="inlineStr">
         <is>
-          <t>De paved road is zelfbedienbaar.</t>
+          <t>On-road keuzes hoeven niet te worden beoordeeld.</t>
         </is>
       </c>
       <c r="E10" s="131" t="n"/>
-      <c r="G10" s="85" t="inlineStr">
-        <is>
-          <t>Pervasive</t>
-        </is>
-      </c>
-      <c r="H10" s="85">
-        <f>COUNTIF(C13:C14,"✔")</f>
-        <v/>
-      </c>
-      <c r="I10" s="85" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="85">
-        <f>IF(H10=I10,1,0)</f>
-        <v/>
-      </c>
-      <c r="K10" s="85">
-        <f>J10*K9</f>
-        <v/>
-      </c>
+      <c r="G10" s="85" t="n"/>
+      <c r="H10" s="85" t="n"/>
+      <c r="I10" s="85" t="n"/>
+      <c r="J10" s="85" t="n"/>
+      <c r="K10" s="85" t="n"/>
     </row>
     <row r="11" ht="35" customHeight="1" s="86">
       <c r="B11" s="127" t="inlineStr">
         <is>
-          <t>3. Adopted</t>
-        </is>
-      </c>
-      <c r="C11" s="233" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
+          <t>3. Evoluerend</t>
+        </is>
+      </c>
+      <c r="C11" s="233" t="n"/>
       <c r="D11" s="220" t="inlineStr">
         <is>
-          <t>Teams bouwen standaard op de paved road.</t>
+          <t>De goedgekeurde route wordt continu verbreed en gesnoeid.</t>
         </is>
       </c>
       <c r="E11" s="130">
         <f>COUNTIF(C11:C12,"✔")&amp;" / 2"</f>
         <v/>
       </c>
-      <c r="G11" s="85" t="inlineStr">
-        <is>
-          <t>Evolving</t>
-        </is>
-      </c>
-      <c r="H11" s="85">
-        <f>COUNTIF(C15:C16,"✔")</f>
-        <v/>
-      </c>
-      <c r="I11" s="85" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" s="85">
-        <f>IF(H11=I11,1,0)</f>
-        <v/>
-      </c>
-      <c r="K11" s="85">
-        <f>J11*K10</f>
-        <v/>
-      </c>
+      <c r="G11" s="85" t="n"/>
+      <c r="H11" s="85" t="n"/>
+      <c r="I11" s="85" t="n"/>
+      <c r="J11" s="85" t="n"/>
+      <c r="K11" s="85" t="n"/>
     </row>
     <row r="12" ht="35" customHeight="1" s="86">
       <c r="B12" s="131" t="n"/>
       <c r="C12" s="234" t="n"/>
       <c r="D12" s="208" t="inlineStr">
         <is>
-          <t>On-road keuzes hoeven niet te worden beoordeeld.</t>
+          <t>Lessen uit beoordelingen worden er in teruggevoerd.</t>
         </is>
       </c>
       <c r="E12" s="131" t="n"/>
-    </row>
-    <row r="13" ht="35" customHeight="1" s="86">
-      <c r="B13" s="185" t="inlineStr">
-        <is>
-          <t>4. Pervasive</t>
-        </is>
-      </c>
-      <c r="C13" s="235" t="n"/>
-      <c r="D13" s="223" t="inlineStr">
-        <is>
-          <t>De paved road is de norm binnen het hele landschap.</t>
-        </is>
-      </c>
-      <c r="E13" s="188">
-        <f>COUNTIF(C13:C14,"✔")&amp;" / 2"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="35" customHeight="1" s="86">
-      <c r="B14" s="131" t="n"/>
-      <c r="C14" s="236" t="n"/>
-      <c r="D14" s="210" t="inlineStr">
-        <is>
-          <t>Afwijken van de paved road is de zeldzame, verantwoorde uitzondering.</t>
-        </is>
-      </c>
-      <c r="E14" s="131" t="n"/>
-    </row>
-    <row r="15" ht="35" customHeight="1" s="86">
-      <c r="B15" s="127" t="inlineStr">
-        <is>
-          <t>5. Evolving</t>
-        </is>
-      </c>
-      <c r="C15" s="233" t="n"/>
-      <c r="D15" s="220" t="inlineStr">
-        <is>
-          <t>De paved road wordt continu verbreed en gesnoeid.</t>
-        </is>
-      </c>
-      <c r="E15" s="130">
-        <f>COUNTIF(C15:C16,"✔")&amp;" / 2"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="35" customHeight="1" s="86">
-      <c r="B16" s="131" t="n"/>
-      <c r="C16" s="234" t="n"/>
-      <c r="D16" s="208" t="inlineStr">
-        <is>
-          <t>Lessen uit beoordelingen worden erin teruggevoerd.</t>
-        </is>
-      </c>
-      <c r="E16" s="131" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="12">
+  <mergeCells count="8">
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="E9:E10"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="E13:E14"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="E15:E16"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="E11:E12"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B15:B16"/>
   </mergeCells>
   <conditionalFormatting sqref="E7:E8">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="3" text="" percent="0" bottom="0">
